--- a/artfynd/A 47348-2022 artfynd.xlsx
+++ b/artfynd/A 47348-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47348-2022 artfynd.xlsx
+++ b/artfynd/A 47348-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99658482</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473821.3799738613</v>
+        <v>473821</v>
       </c>
       <c r="R2" t="n">
-        <v>6884661.690804157</v>
+        <v>6884661</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-04-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-04-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,12 +776,7 @@
         <v>104852203</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473868.6552849098</v>
+        <v>473868</v>
       </c>
       <c r="R3" t="n">
-        <v>6884709.102227872</v>
+        <v>6884709</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -906,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104852235</v>
+        <v>104852211</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473936.9864421724</v>
+        <v>473880</v>
       </c>
       <c r="R4" t="n">
-        <v>6884688.902816636</v>
+        <v>6884696</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1024,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104852211</v>
+        <v>104852222</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473879.8151274031</v>
+        <v>473913</v>
       </c>
       <c r="R5" t="n">
-        <v>6884696.369406677</v>
+        <v>6884706</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1115,7 +1085,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Många bladrosetter.</t>
+          <t>Tät förekomst.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,15 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104852222</v>
+        <v>104852235</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473913.6596766743</v>
+        <v>473937</v>
       </c>
       <c r="R6" t="n">
-        <v>6884705.476372882</v>
+        <v>6884689</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1233,7 +1198,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tät förekomst.</t>
+          <t>Många bladrosetter.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 47348-2022 artfynd.xlsx
+++ b/artfynd/A 47348-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99658482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104852203</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104852211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104852222</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,8 +1247,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104852235</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>